--- a/stories/arbres/TREE-COL-006.xlsx
+++ b/stories/arbres/TREE-COL-006.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Iris arrive à l'école avec maman. La cloche est douce. Iris range son manteau. La maîtresse sourit. Iris a une idée. Elle lève la main. Elle attend. Puis elle pourra parler. Maman dit au revoir, tout près de la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le tapis, la table, ou la fenêtre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Iris s'assoit sur le tapis. Le tissu est chaud. Elle lève la main. Elle attend. Un camarade parle. Puis la maîtresse dit : Iris. Iris parle. Elle dit : le tapis est doux.</t>
+          <t>Iris s'assoit sur le tapis. Le tissu est chaud. Elle lève la main. Elle attend. Un camarade parle. Puis Iris. Iris parle. Le tapis est doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,14 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Iris s'assoit sur le tapis. Le tissu est chaud. Elle lève la main. Elle attend. Un camarade parle. Puis
+maitresse|Iris.
+narrateur|Iris parle.
+narrateur|Le tapis est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1860,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Iris est sur le tapis. Que fait-elle avant de parler ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2033,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Iris a attendu. Puis elle a parlé. C'était son tour.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2224,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2203,7 +2253,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>La maîtresse ouvre l'histoire. Iris lève la main. Elle attend. Puis elle parle. Elle dit : le loup est dans le bois.</t>
+          <t>La maîtresse ouvre l'histoire. Iris lève la main. Elle attend. Puis elle parle. Le loup est dans le bois.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2341,6 +2391,12 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|La maîtresse ouvre l'histoire. Iris lève la main. Elle attend. Puis elle parle.
+narrateur|Le loup est dans le bois.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2585,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2754,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et l'histoire. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2921,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3088,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et l'histoire. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3255,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3422,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et l'histoire. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3589,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3618,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>On chante tout doux. Iris attend. Puis elle parle. Elle dit : j'aime le refrain.</t>
+          <t>On chante tout doux. Iris attend. Puis elle parle. J'aime le refrain.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3756,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|On chante tout doux. Iris attend. Puis elle parle.
+narrateur|J'aime le refrain.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3950,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4119,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et la chanson. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4286,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4453,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et la chanson. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4620,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4787,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et la chanson. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4954,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4851,7 +4983,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Iris prend un crayon. Elle lève la main. Elle attend. Puis elle parle. Elle dit : je dessine un soleil.</t>
+          <t>Iris prend un crayon. Elle lève la main. Elle attend. Puis elle parle. Je dessine un soleil.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4989,6 +5121,12 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Iris prend un crayon. Elle lève la main. Elle attend. Puis elle parle.
+narrateur|Je dessine un soleil.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5315,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5484,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et le dessin. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5651,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5818,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et le dessin. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5985,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6152,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et le dessin. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6319,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6348,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Iris s'assoit à la table. Ça sent les crayons. Elle lève la main. Elle attend. Puis elle parle. Elle dit : la table est lisse.</t>
+          <t>Iris s'assoit à la table. Ça sent les crayons. Elle lève la main. Elle attend. Puis elle parle. La table est lisse.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6486,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Iris s'assoit à la table. Ça sent les crayons. Elle lève la main. Elle attend. Puis elle parle.
+narrateur|La table est lisse.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6668,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Iris est à la table. Que fait-elle d'abord ?</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6841,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Attendre, puis parler. La maîtresse a dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6845,6 +7034,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
         </is>
       </c>
     </row>
@@ -7009,6 +7203,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|À la table, l'histoire est posée. Iris attend. Puis elle parle. Elle raconte une phrase.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7197,6 +7396,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7361,6 +7565,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la table et l'histoire. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7523,6 +7732,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7685,6 +7899,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la table et l'histoire. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7847,6 +8066,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8009,6 +8233,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la table et l'histoire. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8171,6 +8400,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8333,6 +8567,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|La chanson commence. Iris attend son tour. Puis elle parle. Elle dit le premier mot.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8521,6 +8760,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8685,6 +8929,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la table et la chanson. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8847,6 +9096,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9009,6 +9263,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la table et la chanson. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9171,6 +9430,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9333,6 +9597,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la table et la chanson. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9495,6 +9764,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9657,6 +9931,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Le dessin est sur la table. Iris attend. Puis elle parle. Elle nomme la couleur bleue.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9845,6 +10124,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10009,6 +10293,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la table et le dessin. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10171,6 +10460,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10333,6 +10627,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la table et le dessin. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10495,6 +10794,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10657,6 +10961,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la table et le dessin. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10819,6 +11128,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10843,7 +11157,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Iris s'assoit près de la fenêtre. La lumière est claire. Elle lève la main. Elle attend. Puis elle parle. Elle dit : je vois un oiseau.</t>
+          <t>Iris s'assoit près de la fenêtre. La lumière est claire. Elle lève la main. Elle attend. Puis elle parle. Je vois un oiseau.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10981,6 +11295,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Iris s'assoit près de la fenêtre. La lumière est claire. Elle lève la main. Elle attend. Puis elle parle.
+narrateur|Je vois un oiseau.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11157,6 +11477,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Iris est près de la fenêtre. Que fait-elle d'abord ?</t>
         </is>
       </c>
     </row>
@@ -11325,6 +11650,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Iris a levé la main. Elle a attendu. Puis elle a parlé.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11513,6 +11843,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
         </is>
       </c>
     </row>
@@ -11677,6 +12012,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Près de la fenêtre, on écoute l'histoire. Iris attend. Puis elle parle. Un oiseau passe.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11865,6 +12205,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12029,6 +12374,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et l'histoire. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12191,6 +12541,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12353,6 +12708,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et l'histoire. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12515,6 +12875,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12677,6 +13042,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et l'histoire. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12839,6 +13209,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12863,7 +13238,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>On chante près de la lumière. Iris attend. Puis elle parle. Elle dit : c'est clair.</t>
+          <t>On chante près de la lumière. Iris attend. Puis elle parle. C'est clair.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13001,6 +13376,12 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|On chante près de la lumière. Iris attend. Puis elle parle.
+narrateur|C'est clair.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13189,6 +13570,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13353,6 +13739,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et la chanson. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13515,6 +13906,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13677,6 +14073,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et la chanson. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13839,6 +14240,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14001,6 +14407,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et la chanson. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14163,6 +14574,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14187,7 +14603,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Iris dessine la fenêtre. Elle attend. Puis elle parle. Elle dit : j'ai fini le toit.</t>
+          <t>Iris dessine la fenêtre. Elle attend. Puis elle parle. J'ai fini le toit.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14325,6 +14741,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Iris dessine la fenêtre. Elle attend. Puis elle parle.
+narrateur|J'ai fini le toit.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14513,6 +14935,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14677,6 +15104,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et le dessin. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14839,6 +15271,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15001,6 +15438,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et le dessin. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15163,6 +15605,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15325,6 +15772,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et le dessin. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15487,6 +15939,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15505,7 +15962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15592,6 +16049,13 @@
       <c r="A12" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-006.xlsx
+++ b/stories/arbres/TREE-COL-006.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Iris arrive à l'école avec maman. La cloche est douce. Iris range son manteau. La maîtresse sourit. Iris a une idée. Elle lève la main. Elle attend. Puis elle pourra parler. Maman dit au revoir, tout près de la porte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le tapis, la table, ou la fenêtre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1684,6 +1691,7 @@
 narrateur|Le tapis est doux.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1867,6 +1875,7 @@
           <t>narrateur|Iris est sur le tapis. Que fait-elle avant de parler ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2038,6 +2047,7 @@
           <t>narrateur|Iris a attendu. Puis elle a parlé. C'était son tour.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2229,6 +2239,7 @@
           <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2397,6 +2408,7 @@
 narrateur|Le loup est dans le bois.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2592,6 +2604,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2759,6 +2772,7 @@
           <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et l'histoire. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2926,6 +2940,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3093,6 +3108,7 @@
           <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et l'histoire. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3260,6 +3276,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3427,6 +3444,7 @@
           <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et l'histoire. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3594,6 +3612,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3781,7 @@
 narrateur|J'aime le refrain.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3957,6 +3977,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
           <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et la chanson. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4481,7 @@
           <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et la chanson. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4817,7 @@
           <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et la chanson. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4985,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5127,6 +5154,7 @@
 narrateur|Je dessine un soleil.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5322,6 +5350,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5489,6 +5518,7 @@
           <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et le dessin. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5656,6 +5686,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5823,6 +5854,7 @@
           <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et le dessin. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5990,6 +6022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6157,6 +6190,7 @@
           <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et le dessin. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6324,6 +6358,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6492,6 +6527,7 @@
 narrateur|La table est lisse.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6675,6 +6711,7 @@
           <t>narrateur|Iris est à la table. Que fait-elle d'abord ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6846,6 +6883,7 @@
           <t>narrateur|Oui. Attendre, puis parler. La maîtresse a dit son nom.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7041,6 +7079,7 @@
           <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7208,6 +7247,7 @@
           <t>narrateur|À la table, l'histoire est posée. Iris attend. Puis elle parle. Elle raconte une phrase.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7403,6 +7443,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7570,6 +7611,7 @@
           <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la table et l'histoire. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7737,6 +7779,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7904,6 +7947,7 @@
           <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la table et l'histoire. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8071,6 +8115,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8238,6 +8283,7 @@
           <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la table et l'histoire. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8405,6 +8451,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8572,6 +8619,7 @@
           <t>narrateur|La chanson commence. Iris attend son tour. Puis elle parle. Elle dit le premier mot.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8767,6 +8815,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8934,6 +8983,7 @@
           <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la table et la chanson. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9101,6 +9151,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9268,6 +9319,7 @@
           <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la table et la chanson. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9435,6 +9487,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9602,6 +9655,7 @@
           <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la table et la chanson. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9769,6 +9823,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9936,6 +9991,7 @@
           <t>narrateur|Le dessin est sur la table. Iris attend. Puis elle parle. Elle nomme la couleur bleue.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10131,6 +10187,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10298,6 +10355,7 @@
           <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la table et le dessin. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10465,6 +10523,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10632,6 +10691,7 @@
           <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la table et le dessin. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10799,6 +10859,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10966,6 +11027,7 @@
           <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la table et le dessin. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11133,6 +11195,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11301,6 +11364,7 @@
 narrateur|Je vois un oiseau.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11484,6 +11548,7 @@
           <t>narrateur|Iris est près de la fenêtre. Que fait-elle d'abord ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11655,6 +11720,7 @@
           <t>narrateur|Iris a levé la main. Elle a attendu. Puis elle a parlé.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11850,6 +11916,7 @@
           <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12017,6 +12084,7 @@
           <t>narrateur|Près de la fenêtre, on écoute l'histoire. Iris attend. Puis elle parle. Un oiseau passe.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12212,6 +12280,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12379,6 +12448,7 @@
           <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et l'histoire. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12546,6 +12616,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12713,6 +12784,7 @@
           <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et l'histoire. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12880,6 +12952,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13047,6 +13120,7 @@
           <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et l'histoire. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13214,6 +13288,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13382,6 +13457,7 @@
 narrateur|C'est clair.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13577,6 +13653,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13744,6 +13821,7 @@
           <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et la chanson. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13911,6 +13989,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14078,6 +14157,7 @@
           <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et la chanson. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14245,6 +14325,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14412,6 +14493,7 @@
           <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et la chanson. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14579,6 +14661,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14747,6 +14830,7 @@
 narrateur|J'ai fini le toit.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14942,6 +15026,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15109,6 +15194,7 @@
           <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et le dessin. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15276,6 +15362,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15443,6 +15530,7 @@
           <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et le dessin. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15610,6 +15698,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15777,6 +15866,7 @@
           <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et le dessin. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15944,6 +16034,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15962,7 +16053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16056,6 +16147,20 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16070,7 +16175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16257,6 +16362,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-006.xlsx
+++ b/stories/arbres/TREE-COL-006.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Iris attend son tour de parole</t>
+          <t>Le rayon du vestiaire de Mila</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un rayon danse dans la poussière du vestiaire. Mila lève la main, elle attend, puis elle parle, sur le tapis, à la table ou près de la fenêtre.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Iris arrive à l'école avec maman. La cloche est douce. Iris range son manteau. La maîtresse sourit. Iris a une idée. Elle lève la main. Elle attend. Puis elle pourra parler. Maman dit au revoir, tout près de la porte.</t>
+          <t>Un rayon passe entre deux manteaux, au vestiaire. Il tient un peu de poussière, comme de la neige. Les crochets sont froids, tout gris. Un cartable bleu penche, un peu trop. Dedans, une poire attend dans un sachet. Le sachet fait un bruit de papier. Dehors, une flaque ronde garde un morceau de ciel. La cloche n'a pas encore sonné. Maman plie l'écharpe rouge, tout doux. Papa pose le cartable contre le mur. Tu as vu la poussière dans la lumière, Mila ? Oui. Elle danse. La poire est pour plus tard. Il faut attendre, d'accord ? D'accord, papa. En ce moment, Mila accroche son manteau. Le crochet fait un petit clic. Tu lèves la main, si tu as une idée. Tu attends. Puis parler. J'attends. Puis je parle. Bravo, Mila. La classe sent encore le savon des lavabos. Bonne journée, ma puce. Au revoir, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,7 +1337,33 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Iris arrive à l'école avec maman. La cloche est douce. Iris range son manteau. La maîtresse sourit. Iris a une idée. Elle lève la main. Elle attend. Puis elle pourra parler. Maman dit au revoir, tout près de la porte.</t>
+          <t>narrateur|Un rayon passe entre deux manteaux, au vestiaire.
+narrateur|Il tient un peu de poussière, comme de la neige.
+narrateur|Les crochets sont froids, tout gris.
+narrateur|Un cartable bleu penche, un peu trop.
+narrateur|Dedans, une poire attend dans un sachet.
+narrateur|Le sachet fait un bruit de papier.
+narrateur|Dehors, une flaque ronde garde un morceau de ciel.
+narrateur|La cloche n'a pas encore sonné.
+narrateur|Maman plie l'écharpe rouge, tout doux.
+narrateur|Papa pose le cartable contre le mur.
+maman|Tu as vu la poussière dans la lumière, Mila ?
+enfant-f|Oui.
+enfant-f|Elle danse.
+papa|La poire est pour plus tard.
+papa|Il faut attendre, d'accord ?
+enfant-f|D'accord, papa.
+narrateur|En ce moment, Mila accroche son manteau.
+narrateur|Le crochet fait un petit clic.
+maman|Tu lèves la main, si tu as une idée.
+maman|Tu attends.
+papa|Puis parler.
+enfant-f|J'attends.
+enfant-f|Puis je parle.
+papa|Bravo, Mila.
+narrateur|La classe sent encore le savon des lavabos.
+maman|Bonne journée, ma puce.
+enfant-f|Au revoir, maman.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1353,7 +1391,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le tapis, la table, ou la fenêtre.</t>
+          <t>La classe a trois places, pour s'asseoir. Le tapis, la table, ou la fenêtre ? Tu choisis. Ensuite tu attends. Puis parler.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1555,11 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le tapis, la table, ou la fenêtre.</t>
+          <t>narrateur|La classe a trois places, pour s'asseoir.
+papa|Le tapis, la table, ou la fenêtre ?
+maman|Tu choisis.
+maman|Ensuite tu attends.
+maman|Puis parler.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Iris s'assoit sur le tapis. Le tissu est chaud. Elle lève la main. Elle attend. Un camarade parle. Puis Iris. Iris parle. Le tapis est doux.</t>
+          <t>Le tapis de la classe est gris, un peu rêche. Mila s'assoit. Ses genoux font un bruit de laine. Un rayon pose un carré jaune sur le tissu. Qui a une idée ? Mila lève la main. Sa main reste en l'air, toute droite. Il faut attendre, Mila. Puis parler. J'attends. Quelqu'un parle d'abord, tout doux. Mila attend encore. Son cœur bat un peu. Mila, c'est ton tour. Le tapis est chaud ici. Bravo. Tu as attendu. Puis parler. Tu l'as fait. Tu as fait du bon travail ? Oui, maman. Le carré de soleil a bougé, tout lent.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,10 +1727,28 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Iris s'assoit sur le tapis. Le tissu est chaud. Elle lève la main. Elle attend. Un camarade parle. Puis
-maitresse|Iris.
-narrateur|Iris parle.
-narrateur|Le tapis est doux.</t>
+          <t>narrateur|Le tapis de la classe est gris, un peu rêche.
+narrateur|Mila s'assoit.
+narrateur|Ses genoux font un bruit de laine.
+narrateur|Un rayon pose un carré jaune sur le tissu.
+maitresse|Qui a une idée ?
+narrateur|Mila lève la main.
+narrateur|Sa main reste en l'air, toute droite.
+maman|Il faut attendre, Mila.
+papa|Puis parler.
+enfant-f|J'attends.
+narrateur|Quelqu'un parle d'abord, tout doux.
+narrateur|Mila attend encore.
+narrateur|Son cœur bat un peu.
+maitresse|Mila, c'est ton tour.
+enfant-f|Le tapis est chaud ici.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|Tu l'as fait.
+maman|Tu as fait du bon travail ?
+enfant-f|Oui, maman.
+narrateur|Le carré de soleil a bougé, tout lent.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1716,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Iris est sur le tapis. Que fait-elle avant de parler ?</t>
+          <t>Mila est sur le tapis. Que fait-elle avant de parler ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1872,7 +1932,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Iris est sur le tapis. Que fait-elle avant de parler ?</t>
+          <t>narrateur|Mila est sur le tapis.
+maman|Que fait-elle avant de parler ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1900,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Iris a attendu. Puis elle a parlé. C'était son tour.</t>
+          <t>Elle attend. Puis parler. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Le tapis redevient calme, sous ses genoux. Tu as fait du bon travail. Oui, papa.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2044,7 +2105,14 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Iris a attendu. Puis elle a parlé. C'était son tour.</t>
+          <t>papa|Elle attend.
+maman|Puis parler.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maitresse|Bravo, Mila.
+narrateur|Le tapis redevient calme, sous ses genoux.
+papa|Tu as fait du bon travail.
+enfant-f|Oui, papa.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2072,7 +2140,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>Le tapis gris garde encore un carré de soleil. On peut prendre l'histoire, la chanson, ou le dessin. Tu attends ton tour. Puis parler.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2236,7 +2304,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>narrateur|Le tapis gris garde encore un carré de soleil.
+papa|On peut prendre l'histoire, la chanson, ou le dessin.
+maman|Tu attends ton tour.
+papa|Puis parler.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2264,7 +2335,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>La maîtresse ouvre l'histoire. Iris lève la main. Elle attend. Puis elle parle. Le loup est dans le bois.</t>
+          <t>Le tapis gris garde encore un carré de soleil. La maîtresse ouvre l'histoire. Le loup marche dans le bois, sur l'image. Les arbres sont verts, un peu sombres. Qui veut dire un mot ? Mila lève la main. Elle attend. D'abord attendre. Puis parler. J'attends. Un autre mot est dit, tout bas. Mila garde la main en l'air. Mila, à toi. Le loup est dans le bois. Bravo. Tu as attendu. Puis parler. C'est ça. Tu as levé la main ? Oui, maman. La page du loup reste ouverte, un moment.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2404,8 +2475,27 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|La maîtresse ouvre l'histoire. Iris lève la main. Elle attend. Puis elle parle.
-narrateur|Le loup est dans le bois.</t>
+          <t>narrateur|Le tapis gris garde encore un carré de soleil.
+narrateur|La maîtresse ouvre l'histoire.
+narrateur|Le loup marche dans le bois, sur l'image.
+narrateur|Les arbres sont verts, un peu sombres.
+maitresse|Qui veut dire un mot ?
+narrateur|Mila lève la main.
+narrateur|Elle attend.
+papa|D'abord attendre.
+maman|Puis parler.
+enfant-f|J'attends.
+narrateur|Un autre mot est dit, tout bas.
+narrateur|Mila garde la main en l'air.
+maitresse|Mila, à toi.
+enfant-f|Le loup est dans le bois.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|C'est ça.
+maman|Tu as levé la main ?
+enfant-f|Oui, maman.
+narrateur|La page du loup reste ouverte, un moment.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2433,7 +2523,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Le livre reste ouvert, sur le loup du bois. On peut prendre le crayon, le coussin, ou le grelot. Tu attends. Puis parler. Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2601,7 +2691,11 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Le livre reste ouvert, sur le loup du bois.
+maman|On peut prendre le crayon, le coussin, ou le grelot.
+papa|Tu attends.
+papa|Puis parler.
+maman|Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2629,7 +2723,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et l'histoire. Maman l'attend à la porte.</t>
+          <t>Le tapis gris garde encore un carré de soleil. Le livre reste ouvert, sur le loup du bois. Le crayon jaune repose sur le tapis, près du loup. Le crayon jaune sent un peu le bois. La mine est douce, déjà un peu ronde. Le crayon, s'il te plaît. Tu lèves la main, d'abord. Tu attends. Puis parler. Mila lève la main. Elle attend. Mila, tu peux prendre le crayon. Merci. Je parle maintenant. Le crayon est jaune. Bravo. Tu as attendu. Puis parler. C'est bien. Tu as fini d'attendre ton tour ? Oui, papa. Un petit trait jaune reste sur le papier. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2769,7 +2863,29 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et l'histoire. Maman l'attend à la porte.</t>
+          <t>narrateur|Le tapis gris garde encore un carré de soleil.
+narrateur|Le livre reste ouvert, sur le loup du bois.
+narrateur|Le crayon jaune repose sur le tapis, près du loup.
+narrateur|Le crayon jaune sent un peu le bois.
+narrateur|La mine est douce, déjà un peu ronde.
+enfant-f|Le crayon, s'il te plaît.
+maman|Tu lèves la main, d'abord.
+papa|Tu attends.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle attend.
+maitresse|Mila, tu peux prendre le crayon.
+enfant-f|Merci.
+enfant-f|Je parle maintenant.
+enfant-f|Le crayon est jaune.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|C'est bien.
+papa|Tu as fini d'attendre ton tour ?
+enfant-f|Oui, papa.
+narrateur|Un petit trait jaune reste sur le papier.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2797,7 +2913,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu sur le tapis. C'était l'histoire. Elle a pris le crayon. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le crayon jaune a un trait, tout mince, au bout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2937,7 +3053,19 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu sur le tapis.
+narrateur|C'était l'histoire.
+narrateur|Elle a pris le crayon.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le crayon jaune a un trait, tout mince, au bout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2965,7 +3093,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et l'histoire. Maman l'attend à la porte.</t>
+          <t>Le tapis gris garde encore un carré de soleil. Le livre reste ouvert, sur le loup du bois. Le coussin bleu écoute encore l'histoire, tout mou. Le coussin bleu est mou, un peu lourd. Il sent la classe, et un peu le savon. Le coussin. Tu attends, d'abord. Puis parler. Mila lève la main. Le coussin attend aussi. Elle ne le prend pas encore. Mila, c'est toi. Je m'assois. Puis je parle. Le coussin est doux. Bravo. Tu as attendu. Puis parler. Oui. Tu es bien, là ? Oui, maman. Le coussin s'enfonce un peu, sous elle. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3105,7 +3233,29 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et l'histoire. Maman l'attend à la porte.</t>
+          <t>narrateur|Le tapis gris garde encore un carré de soleil.
+narrateur|Le livre reste ouvert, sur le loup du bois.
+narrateur|Le coussin bleu écoute encore l'histoire, tout mou.
+narrateur|Le coussin bleu est mou, un peu lourd.
+narrateur|Il sent la classe, et un peu le savon.
+enfant-f|Le coussin.
+papa|Tu attends, d'abord.
+maman|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Le coussin attend aussi.
+narrateur|Elle ne le prend pas encore.
+maitresse|Mila, c'est toi.
+enfant-f|Je m'assois.
+enfant-f|Puis je parle.
+enfant-f|Le coussin est doux.
+maman|Bravo.
+maman|Tu as attendu.
+papa|Puis parler.
+papa|Oui.
+maman|Tu es bien, là ?
+enfant-f|Oui, maman.
+narrateur|Le coussin s'enfonce un peu, sous elle.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3133,7 +3283,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu sur le tapis. C'était l'histoire. Elle a pris le coussin. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le coussin bleu garde encore la forme de Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3273,7 +3423,19 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu sur le tapis.
+narrateur|C'était l'histoire.
+narrateur|Elle a pris le coussin.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le coussin bleu garde encore la forme de Mila.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3301,7 +3463,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et l'histoire. Maman l'attend à la porte.</t>
+          <t>Le tapis gris garde encore un carré de soleil. Le livre reste ouvert, sur le loup du bois. Le grelot reste sage, pendant que le loup marche. Le grelot est petit, tout brillant. Il tient au bout d'un fil rouge. Le grelot. On attend, d'abord. Puis parler. Mila lève la main. Elle n'agite pas le fil. Le grelot reste silencieux. Mila, tu peux. Cling. C'est mon tour. Le grelot chante. Bravo. Tu as attendu. Puis parler. Et tu as sonné. C'était le moment ? Oui, papa. Le fil rouge redevient immobile. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3441,7 +3603,29 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et l'histoire. Maman l'attend à la porte.</t>
+          <t>narrateur|Le tapis gris garde encore un carré de soleil.
+narrateur|Le livre reste ouvert, sur le loup du bois.
+narrateur|Le grelot reste sage, pendant que le loup marche.
+narrateur|Le grelot est petit, tout brillant.
+narrateur|Il tient au bout d'un fil rouge.
+enfant-f|Le grelot.
+maman|On attend, d'abord.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle n'agite pas le fil.
+narrateur|Le grelot reste silencieux.
+maitresse|Mila, tu peux.
+enfant-f|Cling.
+enfant-f|C'est mon tour.
+enfant-f|Le grelot chante.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|Et tu as sonné.
+papa|C'était le moment ?
+enfant-f|Oui, papa.
+narrateur|Le fil rouge redevient immobile.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3469,7 +3653,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu sur le tapis. C'était l'histoire. Elle a pris le grelot. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le fil rouge du grelot ne bouge plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3609,7 +3793,19 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu sur le tapis.
+narrateur|C'était l'histoire.
+narrateur|Elle a pris le grelot.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le fil rouge du grelot ne bouge plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3637,7 +3833,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>On chante tout doux. Iris attend. Puis elle parle. J'aime le refrain.</t>
+          <t>Le tapis gris garde encore un carré de soleil. On chante tout doux, dans la classe. La chanson parle d'une pluie, d'un toit. Mila connaît un mot. Elle lève la main. Tu attends ton tour. Puis parler. J'attends. La chanson continue. Mila n'interrompt pas. Ses pieds restent sages, sous elle. Mila, tu peux dire le mot. Le toit. C'est clair. Bravo. Tu as su attendre. Puis parler. Bien. C'était ton tour ? Oui, papa. Un dernier air reste, tout petit, dans l'air.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3777,8 +3973,27 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|On chante tout doux. Iris attend. Puis elle parle.
-narrateur|J'aime le refrain.</t>
+          <t>narrateur|Le tapis gris garde encore un carré de soleil.
+narrateur|On chante tout doux, dans la classe.
+narrateur|La chanson parle d'une pluie, d'un toit.
+narrateur|Mila connaît un mot.
+narrateur|Elle lève la main.
+maman|Tu attends ton tour.
+papa|Puis parler.
+enfant-f|J'attends.
+narrateur|La chanson continue.
+narrateur|Mila n'interrompt pas.
+narrateur|Ses pieds restent sages, sous elle.
+maitresse|Mila, tu peux dire le mot.
+enfant-f|Le toit.
+enfant-f|C'est clair.
+papa|Bravo.
+papa|Tu as su attendre.
+maman|Puis parler.
+maman|Bien.
+papa|C'était ton tour ?
+enfant-f|Oui, papa.
+narrateur|Un dernier air reste, tout petit, dans l'air.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3806,7 +4021,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Un air tout petit reste dans la classe. On peut prendre le crayon, le coussin, ou le grelot. Tu attends. Puis parler. Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3974,7 +4189,11 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Un air tout petit reste dans la classe.
+maman|On peut prendre le crayon, le coussin, ou le grelot.
+papa|Tu attends.
+papa|Puis parler.
+maman|Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4002,7 +4221,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et la chanson. Maman l'attend à la porte.</t>
+          <t>Le tapis gris garde encore un carré de soleil. Un air tout petit reste dans la classe. Le crayon dessine une goutte, pendant la chanson. Le crayon jaune sent un peu le bois. La mine est douce, déjà un peu ronde. Le crayon, s'il te plaît. Tu lèves la main, d'abord. Tu attends. Puis parler. Mila lève la main. Elle attend. Mila, tu peux prendre le crayon. Merci. Je parle maintenant. Le crayon est jaune. Bravo. Tu as attendu. Puis parler. C'est bien. Tu as fini d'attendre ton tour ? Oui, papa. Un petit trait jaune reste sur le papier. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4142,7 +4361,29 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et la chanson. Maman l'attend à la porte.</t>
+          <t>narrateur|Le tapis gris garde encore un carré de soleil.
+narrateur|Un air tout petit reste dans la classe.
+narrateur|Le crayon dessine une goutte, pendant la chanson.
+narrateur|Le crayon jaune sent un peu le bois.
+narrateur|La mine est douce, déjà un peu ronde.
+enfant-f|Le crayon, s'il te plaît.
+maman|Tu lèves la main, d'abord.
+papa|Tu attends.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle attend.
+maitresse|Mila, tu peux prendre le crayon.
+enfant-f|Merci.
+enfant-f|Je parle maintenant.
+enfant-f|Le crayon est jaune.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|C'est bien.
+papa|Tu as fini d'attendre ton tour ?
+enfant-f|Oui, papa.
+narrateur|Un petit trait jaune reste sur le papier.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4170,7 +4411,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu sur le tapis. C'était la chanson. Elle a pris le crayon. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le crayon jaune a un trait, tout mince, au bout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4310,7 +4551,19 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu sur le tapis.
+narrateur|C'était la chanson.
+narrateur|Elle a pris le crayon.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le crayon jaune a un trait, tout mince, au bout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4338,7 +4591,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et la chanson. Maman l'attend à la porte.</t>
+          <t>Le tapis gris garde encore un carré de soleil. Un air tout petit reste dans la classe. Le coussin garde le rythme, sous les genoux de Mila. Le coussin bleu est mou, un peu lourd. Il sent la classe, et un peu le savon. Le coussin. Tu attends, d'abord. Puis parler. Mila lève la main. Le coussin attend aussi. Elle ne le prend pas encore. Mila, c'est toi. Je m'assois. Puis je parle. Le coussin est doux. Bravo. Tu as attendu. Puis parler. Oui. Tu es bien, là ? Oui, maman. Le coussin s'enfonce un peu, sous elle. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4478,7 +4731,29 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et la chanson. Maman l'attend à la porte.</t>
+          <t>narrateur|Le tapis gris garde encore un carré de soleil.
+narrateur|Un air tout petit reste dans la classe.
+narrateur|Le coussin garde le rythme, sous les genoux de Mila.
+narrateur|Le coussin bleu est mou, un peu lourd.
+narrateur|Il sent la classe, et un peu le savon.
+enfant-f|Le coussin.
+papa|Tu attends, d'abord.
+maman|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Le coussin attend aussi.
+narrateur|Elle ne le prend pas encore.
+maitresse|Mila, c'est toi.
+enfant-f|Je m'assois.
+enfant-f|Puis je parle.
+enfant-f|Le coussin est doux.
+maman|Bravo.
+maman|Tu as attendu.
+papa|Puis parler.
+papa|Oui.
+maman|Tu es bien, là ?
+enfant-f|Oui, maman.
+narrateur|Le coussin s'enfonce un peu, sous elle.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4506,7 +4781,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu sur le tapis. C'était la chanson. Elle a pris le coussin. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le coussin bleu garde encore la forme de Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4646,7 +4921,19 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu sur le tapis.
+narrateur|C'était la chanson.
+narrateur|Elle a pris le coussin.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le coussin bleu garde encore la forme de Mila.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4674,7 +4961,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et la chanson. Maman l'attend à la porte.</t>
+          <t>Le tapis gris garde encore un carré de soleil. Un air tout petit reste dans la classe. Le grelot attend la fin de l'air, sans sonner. Le grelot est petit, tout brillant. Il tient au bout d'un fil rouge. Le grelot. On attend, d'abord. Puis parler. Mila lève la main. Elle n'agite pas le fil. Le grelot reste silencieux. Mila, tu peux. Cling. C'est mon tour. Le grelot chante. Bravo. Tu as attendu. Puis parler. Et tu as sonné. C'était le moment ? Oui, papa. Le fil rouge redevient immobile. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4814,7 +5101,29 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et la chanson. Maman l'attend à la porte.</t>
+          <t>narrateur|Le tapis gris garde encore un carré de soleil.
+narrateur|Un air tout petit reste dans la classe.
+narrateur|Le grelot attend la fin de l'air, sans sonner.
+narrateur|Le grelot est petit, tout brillant.
+narrateur|Il tient au bout d'un fil rouge.
+enfant-f|Le grelot.
+maman|On attend, d'abord.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle n'agite pas le fil.
+narrateur|Le grelot reste silencieux.
+maitresse|Mila, tu peux.
+enfant-f|Cling.
+enfant-f|C'est mon tour.
+enfant-f|Le grelot chante.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|Et tu as sonné.
+papa|C'était le moment ?
+enfant-f|Oui, papa.
+narrateur|Le fil rouge redevient immobile.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4842,7 +5151,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu sur le tapis. C'était la chanson. Elle a pris le grelot. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le fil rouge du grelot ne bouge plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4982,7 +5291,19 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu sur le tapis.
+narrateur|C'était la chanson.
+narrateur|Elle a pris le grelot.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le fil rouge du grelot ne bouge plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5010,7 +5331,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Iris prend un crayon. Elle lève la main. Elle attend. Puis elle parle. Je dessine un soleil.</t>
+          <t>Le tapis gris garde encore un carré de soleil. Un papier blanc attend sur le bois. Une gomme sent le caoutchouc, tout près. Mila a une couleur dans la tête. Elle lève la main. Il faut attendre. Puis parler. J'attends. Quelqu'un nomme le rouge, d'abord. Mila attend. Sa main ne descend pas. Mila, c'est ton tour. Moi, le bleu. Bravo. Tu as attendu. Puis parler. Très bien. Tu as dit le bleu ? Oui, maman. Un trait bleu commence, tout mince, sur le papier.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5150,8 +5471,26 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Iris prend un crayon. Elle lève la main. Elle attend. Puis elle parle.
-narrateur|Je dessine un soleil.</t>
+          <t>narrateur|Le tapis gris garde encore un carré de soleil.
+narrateur|Un papier blanc attend sur le bois.
+narrateur|Une gomme sent le caoutchouc, tout près.
+narrateur|Mila a une couleur dans la tête.
+narrateur|Elle lève la main.
+papa|Il faut attendre.
+maman|Puis parler.
+enfant-f|J'attends.
+narrateur|Quelqu'un nomme le rouge, d'abord.
+narrateur|Mila attend.
+narrateur|Sa main ne descend pas.
+maitresse|Mila, c'est ton tour.
+enfant-f|Moi, le bleu.
+maman|Bravo.
+maman|Tu as attendu.
+papa|Puis parler.
+papa|Très bien.
+maman|Tu as dit le bleu ?
+enfant-f|Oui, maman.
+narrateur|Un trait bleu commence, tout mince, sur le papier.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5179,7 +5518,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Le papier blanc attend encore une couleur. On peut prendre le crayon, le coussin, ou le grelot. Tu attends. Puis parler. Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5347,7 +5686,11 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Le papier blanc attend encore une couleur.
+maman|On peut prendre le crayon, le coussin, ou le grelot.
+papa|Tu attends.
+papa|Puis parler.
+maman|Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5375,7 +5718,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et le dessin. Maman l'attend à la porte.</t>
+          <t>Le tapis gris garde encore un carré de soleil. Le papier blanc attend encore une couleur. Le crayon jaune commence un toit, sur le tapis. Le crayon jaune sent un peu le bois. La mine est douce, déjà un peu ronde. Le crayon, s'il te plaît. Tu lèves la main, d'abord. Tu attends. Puis parler. Mila lève la main. Elle attend. Mila, tu peux prendre le crayon. Merci. Je parle maintenant. Le crayon est jaune. Bravo. Tu as attendu. Puis parler. C'est bien. Tu as fini d'attendre ton tour ? Oui, papa. Un petit trait jaune reste sur le papier. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5515,7 +5858,29 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et le dessin. Maman l'attend à la porte.</t>
+          <t>narrateur|Le tapis gris garde encore un carré de soleil.
+narrateur|Le papier blanc attend encore une couleur.
+narrateur|Le crayon jaune commence un toit, sur le tapis.
+narrateur|Le crayon jaune sent un peu le bois.
+narrateur|La mine est douce, déjà un peu ronde.
+enfant-f|Le crayon, s'il te plaît.
+maman|Tu lèves la main, d'abord.
+papa|Tu attends.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle attend.
+maitresse|Mila, tu peux prendre le crayon.
+enfant-f|Merci.
+enfant-f|Je parle maintenant.
+enfant-f|Le crayon est jaune.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|C'est bien.
+papa|Tu as fini d'attendre ton tour ?
+enfant-f|Oui, papa.
+narrateur|Un petit trait jaune reste sur le papier.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5543,7 +5908,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu sur le tapis. C'était le dessin. Elle a pris le crayon. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le crayon jaune a un trait, tout mince, au bout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5683,7 +6048,19 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu sur le tapis.
+narrateur|C'était le dessin.
+narrateur|Elle a pris le crayon.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le crayon jaune a un trait, tout mince, au bout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5711,7 +6088,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et le dessin. Maman l'attend à la porte.</t>
+          <t>Le tapis gris garde encore un carré de soleil. Le papier blanc attend encore une couleur. Le coussin bleu a un grain de gomme dessus. Le coussin bleu est mou, un peu lourd. Il sent la classe, et un peu le savon. Le coussin. Tu attends, d'abord. Puis parler. Mila lève la main. Le coussin attend aussi. Elle ne le prend pas encore. Mila, c'est toi. Je m'assois. Puis je parle. Le coussin est doux. Bravo. Tu as attendu. Puis parler. Oui. Tu es bien, là ? Oui, maman. Le coussin s'enfonce un peu, sous elle. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5851,7 +6228,29 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et le dessin. Maman l'attend à la porte.</t>
+          <t>narrateur|Le tapis gris garde encore un carré de soleil.
+narrateur|Le papier blanc attend encore une couleur.
+narrateur|Le coussin bleu a un grain de gomme dessus.
+narrateur|Le coussin bleu est mou, un peu lourd.
+narrateur|Il sent la classe, et un peu le savon.
+enfant-f|Le coussin.
+papa|Tu attends, d'abord.
+maman|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Le coussin attend aussi.
+narrateur|Elle ne le prend pas encore.
+maitresse|Mila, c'est toi.
+enfant-f|Je m'assois.
+enfant-f|Puis je parle.
+enfant-f|Le coussin est doux.
+maman|Bravo.
+maman|Tu as attendu.
+papa|Puis parler.
+papa|Oui.
+maman|Tu es bien, là ?
+enfant-f|Oui, maman.
+narrateur|Le coussin s'enfonce un peu, sous elle.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5879,7 +6278,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu sur le tapis. C'était le dessin. Elle a pris le coussin. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le coussin bleu garde encore la forme de Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6019,7 +6418,19 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu sur le tapis.
+narrateur|C'était le dessin.
+narrateur|Elle a pris le coussin.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le coussin bleu garde encore la forme de Mila.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6047,7 +6458,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et le dessin. Maman l'attend à la porte.</t>
+          <t>Le tapis gris garde encore un carré de soleil. Le papier blanc attend encore une couleur. Le grelot brille à côté du papier blanc. Le grelot est petit, tout brillant. Il tient au bout d'un fil rouge. Le grelot. On attend, d'abord. Puis parler. Mila lève la main. Elle n'agite pas le fil. Le grelot reste silencieux. Mila, tu peux. Cling. C'est mon tour. Le grelot chante. Bravo. Tu as attendu. Puis parler. Et tu as sonné. C'était le moment ? Oui, papa. Le fil rouge redevient immobile. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6187,7 +6598,29 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était le tapis et le dessin. Maman l'attend à la porte.</t>
+          <t>narrateur|Le tapis gris garde encore un carré de soleil.
+narrateur|Le papier blanc attend encore une couleur.
+narrateur|Le grelot brille à côté du papier blanc.
+narrateur|Le grelot est petit, tout brillant.
+narrateur|Il tient au bout d'un fil rouge.
+enfant-f|Le grelot.
+maman|On attend, d'abord.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle n'agite pas le fil.
+narrateur|Le grelot reste silencieux.
+maitresse|Mila, tu peux.
+enfant-f|Cling.
+enfant-f|C'est mon tour.
+enfant-f|Le grelot chante.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|Et tu as sonné.
+papa|C'était le moment ?
+enfant-f|Oui, papa.
+narrateur|Le fil rouge redevient immobile.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6215,7 +6648,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu sur le tapis. C'était le dessin. Elle a pris le grelot. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le fil rouge du grelot ne bouge plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6355,7 +6788,19 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu sur le tapis.
+narrateur|C'était le dessin.
+narrateur|Elle a pris le grelot.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le fil rouge du grelot ne bouge plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6383,7 +6828,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Iris s'assoit à la table. Ça sent les crayons. Elle lève la main. Elle attend. Puis elle parle. La table est lisse.</t>
+          <t>La table est ronde, en bois clair. Une craie blanche a laissé un trait. Mila pose les mains à plat. Le bois est froid. On écoute d'abord. Mila lève la main, tout près de l'oreille. Tu attends, Mila. Puis parler. J'attends. Un crayon roule, puis s'arrête. Mila ne parle pas encore. Elle attend. Mila, tu peux parler. Le bois est lisse. Bravo. Tu as su attendre. Puis parler. C'est bien. Tu as fini d'attendre ton tour ? Oui, papa. Le trait de craie brille, tout petit.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6523,8 +6968,27 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Iris s'assoit à la table. Ça sent les crayons. Elle lève la main. Elle attend. Puis elle parle.
-narrateur|La table est lisse.</t>
+          <t>narrateur|La table est ronde, en bois clair.
+narrateur|Une craie blanche a laissé un trait.
+narrateur|Mila pose les mains à plat.
+narrateur|Le bois est froid.
+maitresse|On écoute d'abord.
+narrateur|Mila lève la main, tout près de l'oreille.
+papa|Tu attends, Mila.
+maman|Puis parler.
+enfant-f|J'attends.
+narrateur|Un crayon roule, puis s'arrête.
+narrateur|Mila ne parle pas encore.
+narrateur|Elle attend.
+maitresse|Mila, tu peux parler.
+enfant-f|Le bois est lisse.
+maman|Bravo.
+maman|Tu as su attendre.
+papa|Puis parler.
+papa|C'est bien.
+papa|Tu as fini d'attendre ton tour ?
+enfant-f|Oui, papa.
+narrateur|Le trait de craie brille, tout petit.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6552,7 +7016,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Iris est à la table. Que fait-elle d'abord ?</t>
+          <t>Mila est à la table. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6708,7 +7172,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Iris est à la table. Que fait-elle d'abord ?</t>
+          <t>narrateur|Mila est à la table.
+papa|Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6736,7 +7201,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Attendre, puis parler. La maîtresse a dit son nom.</t>
+          <t>Elle attend. Puis parler. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Le crayon ne roule plus, sur le bois. Tu as fait du bon travail. Oui, maman.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6880,7 +7345,14 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Attendre, puis parler. La maîtresse a dit son nom.</t>
+          <t>maman|Elle attend.
+papa|Puis parler.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maitresse|Bravo, Mila.
+narrateur|Le crayon ne roule plus, sur le bois.
+maman|Tu as fait du bon travail.
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6908,7 +7380,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>La table de bois reste lisse, un peu froide. On peut prendre l'histoire, la chanson, ou le dessin. Tu attends ton tour. Puis parler.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7076,7 +7548,10 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>narrateur|La table de bois reste lisse, un peu froide.
+papa|On peut prendre l'histoire, la chanson, ou le dessin.
+maman|Tu attends ton tour.
+papa|Puis parler.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7104,7 +7579,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>À la table, l'histoire est posée. Iris attend. Puis elle parle. Elle raconte une phrase.</t>
+          <t>La table de bois reste lisse, un peu froide. La maîtresse ouvre l'histoire. Le loup marche dans le bois, sur l'image. Les arbres sont verts, un peu sombres. Qui veut dire un mot ? Mila lève la main. Elle attend. D'abord attendre. Puis parler. J'attends. Un autre mot est dit, tout bas. Mila garde la main en l'air. Mila, à toi. Le loup est dans le bois. Bravo. Tu as attendu. Puis parler. C'est ça. Tu as levé la main ? Oui, maman. La page du loup reste ouverte, un moment.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7244,7 +7719,27 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|À la table, l'histoire est posée. Iris attend. Puis elle parle. Elle raconte une phrase.</t>
+          <t>narrateur|La table de bois reste lisse, un peu froide.
+narrateur|La maîtresse ouvre l'histoire.
+narrateur|Le loup marche dans le bois, sur l'image.
+narrateur|Les arbres sont verts, un peu sombres.
+maitresse|Qui veut dire un mot ?
+narrateur|Mila lève la main.
+narrateur|Elle attend.
+papa|D'abord attendre.
+maman|Puis parler.
+enfant-f|J'attends.
+narrateur|Un autre mot est dit, tout bas.
+narrateur|Mila garde la main en l'air.
+maitresse|Mila, à toi.
+enfant-f|Le loup est dans le bois.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|C'est ça.
+maman|Tu as levé la main ?
+enfant-f|Oui, maman.
+narrateur|La page du loup reste ouverte, un moment.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7272,7 +7767,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Le livre reste ouvert, sur le loup du bois. On peut prendre le crayon, le coussin, ou le grelot. Tu attends. Puis parler. Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7440,7 +7935,11 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Le livre reste ouvert, sur le loup du bois.
+maman|On peut prendre le crayon, le coussin, ou le grelot.
+papa|Tu attends.
+papa|Puis parler.
+maman|Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7468,7 +7967,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la table et l'histoire. Maman l'attend à la porte.</t>
+          <t>La table de bois reste lisse, un peu froide. Le livre reste ouvert, sur le loup du bois. Le crayon s'arrête au bord de la table, près du livre. Le crayon jaune sent un peu le bois. La mine est douce, déjà un peu ronde. Le crayon, s'il te plaît. Tu lèves la main, d'abord. Tu attends. Puis parler. Mila lève la main. Elle attend. Mila, tu peux prendre le crayon. Merci. Je parle maintenant. Le crayon est jaune. Bravo. Tu as attendu. Puis parler. C'est bien. Tu as fini d'attendre ton tour ? Oui, papa. Un petit trait jaune reste sur le papier. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7608,7 +8107,29 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la table et l'histoire. Maman l'attend à la porte.</t>
+          <t>narrateur|La table de bois reste lisse, un peu froide.
+narrateur|Le livre reste ouvert, sur le loup du bois.
+narrateur|Le crayon s'arrête au bord de la table, près du livre.
+narrateur|Le crayon jaune sent un peu le bois.
+narrateur|La mine est douce, déjà un peu ronde.
+enfant-f|Le crayon, s'il te plaît.
+maman|Tu lèves la main, d'abord.
+papa|Tu attends.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle attend.
+maitresse|Mila, tu peux prendre le crayon.
+enfant-f|Merci.
+enfant-f|Je parle maintenant.
+enfant-f|Le crayon est jaune.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|C'est bien.
+papa|Tu as fini d'attendre ton tour ?
+enfant-f|Oui, papa.
+narrateur|Un petit trait jaune reste sur le papier.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7636,7 +8157,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu à la table. C'était l'histoire. Elle a pris le crayon. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le crayon jaune a un trait, tout mince, au bout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7776,7 +8297,19 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu à la table.
+narrateur|C'était l'histoire.
+narrateur|Elle a pris le crayon.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le crayon jaune a un trait, tout mince, au bout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7804,7 +8337,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la table et l'histoire. Maman l'attend à la porte.</t>
+          <t>La table de bois reste lisse, un peu froide. Le livre reste ouvert, sur le loup du bois. Le coussin est posé sur la chaise, pendant l'histoire. Le coussin bleu est mou, un peu lourd. Il sent la classe, et un peu le savon. Le coussin. Tu attends, d'abord. Puis parler. Mila lève la main. Le coussin attend aussi. Elle ne le prend pas encore. Mila, c'est toi. Je m'assois. Puis je parle. Le coussin est doux. Bravo. Tu as attendu. Puis parler. Oui. Tu es bien, là ? Oui, maman. Le coussin s'enfonce un peu, sous elle. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7944,7 +8477,29 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la table et l'histoire. Maman l'attend à la porte.</t>
+          <t>narrateur|La table de bois reste lisse, un peu froide.
+narrateur|Le livre reste ouvert, sur le loup du bois.
+narrateur|Le coussin est posé sur la chaise, pendant l'histoire.
+narrateur|Le coussin bleu est mou, un peu lourd.
+narrateur|Il sent la classe, et un peu le savon.
+enfant-f|Le coussin.
+papa|Tu attends, d'abord.
+maman|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Le coussin attend aussi.
+narrateur|Elle ne le prend pas encore.
+maitresse|Mila, c'est toi.
+enfant-f|Je m'assois.
+enfant-f|Puis je parle.
+enfant-f|Le coussin est doux.
+maman|Bravo.
+maman|Tu as attendu.
+papa|Puis parler.
+papa|Oui.
+maman|Tu es bien, là ?
+enfant-f|Oui, maman.
+narrateur|Le coussin s'enfonce un peu, sous elle.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7972,7 +8527,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu à la table. C'était l'histoire. Elle a pris le coussin. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le coussin bleu garde encore la forme de Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8112,7 +8667,19 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu à la table.
+narrateur|C'était l'histoire.
+narrateur|Elle a pris le coussin.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le coussin bleu garde encore la forme de Mila.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8140,7 +8707,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la table et l'histoire. Maman l'attend à la porte.</t>
+          <t>La table de bois reste lisse, un peu froide. Le livre reste ouvert, sur le loup du bois. Le grelot fait un cling tout petit, après le loup. Le grelot est petit, tout brillant. Il tient au bout d'un fil rouge. Le grelot. On attend, d'abord. Puis parler. Mila lève la main. Elle n'agite pas le fil. Le grelot reste silencieux. Mila, tu peux. Cling. C'est mon tour. Le grelot chante. Bravo. Tu as attendu. Puis parler. Et tu as sonné. C'était le moment ? Oui, papa. Le fil rouge redevient immobile. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8280,7 +8847,29 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la table et l'histoire. Maman l'attend à la porte.</t>
+          <t>narrateur|La table de bois reste lisse, un peu froide.
+narrateur|Le livre reste ouvert, sur le loup du bois.
+narrateur|Le grelot fait un cling tout petit, après le loup.
+narrateur|Le grelot est petit, tout brillant.
+narrateur|Il tient au bout d'un fil rouge.
+enfant-f|Le grelot.
+maman|On attend, d'abord.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle n'agite pas le fil.
+narrateur|Le grelot reste silencieux.
+maitresse|Mila, tu peux.
+enfant-f|Cling.
+enfant-f|C'est mon tour.
+enfant-f|Le grelot chante.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|Et tu as sonné.
+papa|C'était le moment ?
+enfant-f|Oui, papa.
+narrateur|Le fil rouge redevient immobile.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8308,7 +8897,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu à la table. C'était l'histoire. Elle a pris le grelot. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le fil rouge du grelot ne bouge plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8448,7 +9037,19 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu à la table.
+narrateur|C'était l'histoire.
+narrateur|Elle a pris le grelot.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le fil rouge du grelot ne bouge plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8476,7 +9077,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>La chanson commence. Iris attend son tour. Puis elle parle. Elle dit le premier mot.</t>
+          <t>La table de bois reste lisse, un peu froide. On chante tout doux, dans la classe. La chanson parle d'une pluie, d'un toit. Mila connaît un mot. Elle lève la main. Tu attends ton tour. Puis parler. J'attends. La chanson continue. Mila n'interrompt pas. Ses pieds restent sages, sous elle. Mila, tu peux dire le mot. Le toit. C'est clair. Bravo. Tu as su attendre. Puis parler. Bien. C'était ton tour ? Oui, papa. Un dernier air reste, tout petit, dans l'air.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8616,7 +9217,27 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|La chanson commence. Iris attend son tour. Puis elle parle. Elle dit le premier mot.</t>
+          <t>narrateur|La table de bois reste lisse, un peu froide.
+narrateur|On chante tout doux, dans la classe.
+narrateur|La chanson parle d'une pluie, d'un toit.
+narrateur|Mila connaît un mot.
+narrateur|Elle lève la main.
+maman|Tu attends ton tour.
+papa|Puis parler.
+enfant-f|J'attends.
+narrateur|La chanson continue.
+narrateur|Mila n'interrompt pas.
+narrateur|Ses pieds restent sages, sous elle.
+maitresse|Mila, tu peux dire le mot.
+enfant-f|Le toit.
+enfant-f|C'est clair.
+papa|Bravo.
+papa|Tu as su attendre.
+maman|Puis parler.
+maman|Bien.
+papa|C'était ton tour ?
+enfant-f|Oui, papa.
+narrateur|Un dernier air reste, tout petit, dans l'air.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8644,7 +9265,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Un air tout petit reste dans la classe. On peut prendre le crayon, le coussin, ou le grelot. Tu attends. Puis parler. Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8812,7 +9433,11 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Un air tout petit reste dans la classe.
+maman|On peut prendre le crayon, le coussin, ou le grelot.
+papa|Tu attends.
+papa|Puis parler.
+maman|Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8840,7 +9465,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la table et la chanson. Maman l'attend à la porte.</t>
+          <t>La table de bois reste lisse, un peu froide. Un air tout petit reste dans la classe. Le crayon tapote le bois, sans couper la chanson. Le crayon jaune sent un peu le bois. La mine est douce, déjà un peu ronde. Le crayon, s'il te plaît. Tu lèves la main, d'abord. Tu attends. Puis parler. Mila lève la main. Elle attend. Mila, tu peux prendre le crayon. Merci. Je parle maintenant. Le crayon est jaune. Bravo. Tu as attendu. Puis parler. C'est bien. Tu as fini d'attendre ton tour ? Oui, papa. Un petit trait jaune reste sur le papier. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8980,7 +9605,29 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la table et la chanson. Maman l'attend à la porte.</t>
+          <t>narrateur|La table de bois reste lisse, un peu froide.
+narrateur|Un air tout petit reste dans la classe.
+narrateur|Le crayon tapote le bois, sans couper la chanson.
+narrateur|Le crayon jaune sent un peu le bois.
+narrateur|La mine est douce, déjà un peu ronde.
+enfant-f|Le crayon, s'il te plaît.
+maman|Tu lèves la main, d'abord.
+papa|Tu attends.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle attend.
+maitresse|Mila, tu peux prendre le crayon.
+enfant-f|Merci.
+enfant-f|Je parle maintenant.
+enfant-f|Le crayon est jaune.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|C'est bien.
+papa|Tu as fini d'attendre ton tour ?
+enfant-f|Oui, papa.
+narrateur|Un petit trait jaune reste sur le papier.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9008,7 +9655,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu à la table. C'était la chanson. Elle a pris le crayon. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le crayon jaune a un trait, tout mince, au bout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9148,7 +9795,19 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu à la table.
+narrateur|C'était la chanson.
+narrateur|Elle a pris le crayon.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le crayon jaune a un trait, tout mince, au bout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9176,7 +9835,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la table et la chanson. Maman l'attend à la porte.</t>
+          <t>La table de bois reste lisse, un peu froide. Un air tout petit reste dans la classe. Le coussin est chaud, sous les coudes, pendant l'air. Le coussin bleu est mou, un peu lourd. Il sent la classe, et un peu le savon. Le coussin. Tu attends, d'abord. Puis parler. Mila lève la main. Le coussin attend aussi. Elle ne le prend pas encore. Mila, c'est toi. Je m'assois. Puis je parle. Le coussin est doux. Bravo. Tu as attendu. Puis parler. Oui. Tu es bien, là ? Oui, maman. Le coussin s'enfonce un peu, sous elle. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9316,7 +9975,29 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la table et la chanson. Maman l'attend à la porte.</t>
+          <t>narrateur|La table de bois reste lisse, un peu froide.
+narrateur|Un air tout petit reste dans la classe.
+narrateur|Le coussin est chaud, sous les coudes, pendant l'air.
+narrateur|Le coussin bleu est mou, un peu lourd.
+narrateur|Il sent la classe, et un peu le savon.
+enfant-f|Le coussin.
+papa|Tu attends, d'abord.
+maman|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Le coussin attend aussi.
+narrateur|Elle ne le prend pas encore.
+maitresse|Mila, c'est toi.
+enfant-f|Je m'assois.
+enfant-f|Puis je parle.
+enfant-f|Le coussin est doux.
+maman|Bravo.
+maman|Tu as attendu.
+papa|Puis parler.
+papa|Oui.
+maman|Tu es bien, là ?
+enfant-f|Oui, maman.
+narrateur|Le coussin s'enfonce un peu, sous elle.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9344,7 +10025,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu à la table. C'était la chanson. Elle a pris le coussin. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le coussin bleu garde encore la forme de Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9484,7 +10165,19 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu à la table.
+narrateur|C'était la chanson.
+narrateur|Elle a pris le coussin.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le coussin bleu garde encore la forme de Mila.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9512,7 +10205,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la table et la chanson. Maman l'attend à la porte.</t>
+          <t>La table de bois reste lisse, un peu froide. Un air tout petit reste dans la classe. Le grelot attend, silencieux, jusqu'au dernier mot. Le grelot est petit, tout brillant. Il tient au bout d'un fil rouge. Le grelot. On attend, d'abord. Puis parler. Mila lève la main. Elle n'agite pas le fil. Le grelot reste silencieux. Mila, tu peux. Cling. C'est mon tour. Le grelot chante. Bravo. Tu as attendu. Puis parler. Et tu as sonné. C'était le moment ? Oui, papa. Le fil rouge redevient immobile. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9652,7 +10345,29 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la table et la chanson. Maman l'attend à la porte.</t>
+          <t>narrateur|La table de bois reste lisse, un peu froide.
+narrateur|Un air tout petit reste dans la classe.
+narrateur|Le grelot attend, silencieux, jusqu'au dernier mot.
+narrateur|Le grelot est petit, tout brillant.
+narrateur|Il tient au bout d'un fil rouge.
+enfant-f|Le grelot.
+maman|On attend, d'abord.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle n'agite pas le fil.
+narrateur|Le grelot reste silencieux.
+maitresse|Mila, tu peux.
+enfant-f|Cling.
+enfant-f|C'est mon tour.
+enfant-f|Le grelot chante.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|Et tu as sonné.
+papa|C'était le moment ?
+enfant-f|Oui, papa.
+narrateur|Le fil rouge redevient immobile.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9680,7 +10395,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu à la table. C'était la chanson. Elle a pris le grelot. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le fil rouge du grelot ne bouge plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9820,7 +10535,19 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu à la table.
+narrateur|C'était la chanson.
+narrateur|Elle a pris le grelot.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le fil rouge du grelot ne bouge plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9848,7 +10575,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Le dessin est sur la table. Iris attend. Puis elle parle. Elle nomme la couleur bleue.</t>
+          <t>La table de bois reste lisse, un peu froide. Un papier blanc attend sur le bois. Une gomme sent le caoutchouc, tout près. Mila a une couleur dans la tête. Elle lève la main. Il faut attendre. Puis parler. J'attends. Quelqu'un nomme le rouge, d'abord. Mila attend. Sa main ne descend pas. Mila, c'est ton tour. Moi, le bleu. Bravo. Tu as attendu. Puis parler. Très bien. Tu as dit le bleu ? Oui, maman. Un trait bleu commence, tout mince, sur le papier.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9988,7 +10715,26 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Le dessin est sur la table. Iris attend. Puis elle parle. Elle nomme la couleur bleue.</t>
+          <t>narrateur|La table de bois reste lisse, un peu froide.
+narrateur|Un papier blanc attend sur le bois.
+narrateur|Une gomme sent le caoutchouc, tout près.
+narrateur|Mila a une couleur dans la tête.
+narrateur|Elle lève la main.
+papa|Il faut attendre.
+maman|Puis parler.
+enfant-f|J'attends.
+narrateur|Quelqu'un nomme le rouge, d'abord.
+narrateur|Mila attend.
+narrateur|Sa main ne descend pas.
+maitresse|Mila, c'est ton tour.
+enfant-f|Moi, le bleu.
+maman|Bravo.
+maman|Tu as attendu.
+papa|Puis parler.
+papa|Très bien.
+maman|Tu as dit le bleu ?
+enfant-f|Oui, maman.
+narrateur|Un trait bleu commence, tout mince, sur le papier.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10016,7 +10762,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Le papier blanc attend encore une couleur. On peut prendre le crayon, le coussin, ou le grelot. Tu attends. Puis parler. Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10184,7 +10930,11 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Le papier blanc attend encore une couleur.
+maman|On peut prendre le crayon, le coussin, ou le grelot.
+papa|Tu attends.
+papa|Puis parler.
+maman|Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10212,7 +10962,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la table et le dessin. Maman l'attend à la porte.</t>
+          <t>La table de bois reste lisse, un peu froide. Le papier blanc attend encore une couleur. Le crayon bleu de Mila rejoint le trait de craie. Le crayon jaune sent un peu le bois. La mine est douce, déjà un peu ronde. Le crayon, s'il te plaît. Tu lèves la main, d'abord. Tu attends. Puis parler. Mila lève la main. Elle attend. Mila, tu peux prendre le crayon. Merci. Je parle maintenant. Le crayon est jaune. Bravo. Tu as attendu. Puis parler. C'est bien. Tu as fini d'attendre ton tour ? Oui, papa. Un petit trait jaune reste sur le papier. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10352,7 +11102,29 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la table et le dessin. Maman l'attend à la porte.</t>
+          <t>narrateur|La table de bois reste lisse, un peu froide.
+narrateur|Le papier blanc attend encore une couleur.
+narrateur|Le crayon bleu de Mila rejoint le trait de craie.
+narrateur|Le crayon jaune sent un peu le bois.
+narrateur|La mine est douce, déjà un peu ronde.
+enfant-f|Le crayon, s'il te plaît.
+maman|Tu lèves la main, d'abord.
+papa|Tu attends.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle attend.
+maitresse|Mila, tu peux prendre le crayon.
+enfant-f|Merci.
+enfant-f|Je parle maintenant.
+enfant-f|Le crayon est jaune.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|C'est bien.
+papa|Tu as fini d'attendre ton tour ?
+enfant-f|Oui, papa.
+narrateur|Un petit trait jaune reste sur le papier.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10380,7 +11152,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu à la table. C'était le dessin. Elle a pris le crayon. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le crayon jaune a un trait, tout mince, au bout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10520,7 +11292,19 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu à la table.
+narrateur|C'était le dessin.
+narrateur|Elle a pris le crayon.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le crayon jaune a un trait, tout mince, au bout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10548,7 +11332,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la table et le dessin. Maman l'attend à la porte.</t>
+          <t>La table de bois reste lisse, un peu froide. Le papier blanc attend encore une couleur. Le coussin cale le papier, pour qu'il ne glisse pas. Le coussin bleu est mou, un peu lourd. Il sent la classe, et un peu le savon. Le coussin. Tu attends, d'abord. Puis parler. Mila lève la main. Le coussin attend aussi. Elle ne le prend pas encore. Mila, c'est toi. Je m'assois. Puis je parle. Le coussin est doux. Bravo. Tu as attendu. Puis parler. Oui. Tu es bien, là ? Oui, maman. Le coussin s'enfonce un peu, sous elle. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10688,7 +11472,29 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la table et le dessin. Maman l'attend à la porte.</t>
+          <t>narrateur|La table de bois reste lisse, un peu froide.
+narrateur|Le papier blanc attend encore une couleur.
+narrateur|Le coussin cale le papier, pour qu'il ne glisse pas.
+narrateur|Le coussin bleu est mou, un peu lourd.
+narrateur|Il sent la classe, et un peu le savon.
+enfant-f|Le coussin.
+papa|Tu attends, d'abord.
+maman|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Le coussin attend aussi.
+narrateur|Elle ne le prend pas encore.
+maitresse|Mila, c'est toi.
+enfant-f|Je m'assois.
+enfant-f|Puis je parle.
+enfant-f|Le coussin est doux.
+maman|Bravo.
+maman|Tu as attendu.
+papa|Puis parler.
+papa|Oui.
+maman|Tu es bien, là ?
+enfant-f|Oui, maman.
+narrateur|Le coussin s'enfonce un peu, sous elle.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10716,7 +11522,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu à la table. C'était le dessin. Elle a pris le coussin. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le coussin bleu garde encore la forme de Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10856,7 +11662,19 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu à la table.
+narrateur|C'était le dessin.
+narrateur|Elle a pris le coussin.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le coussin bleu garde encore la forme de Mila.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10884,7 +11702,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la table et le dessin. Maman l'attend à la porte.</t>
+          <t>La table de bois reste lisse, un peu froide. Le papier blanc attend encore une couleur. Le grelot repose près de la gomme, tout calme. Le grelot est petit, tout brillant. Il tient au bout d'un fil rouge. Le grelot. On attend, d'abord. Puis parler. Mila lève la main. Elle n'agite pas le fil. Le grelot reste silencieux. Mila, tu peux. Cling. C'est mon tour. Le grelot chante. Bravo. Tu as attendu. Puis parler. Et tu as sonné. C'était le moment ? Oui, papa. Le fil rouge redevient immobile. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11024,7 +11842,29 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la table et le dessin. Maman l'attend à la porte.</t>
+          <t>narrateur|La table de bois reste lisse, un peu froide.
+narrateur|Le papier blanc attend encore une couleur.
+narrateur|Le grelot repose près de la gomme, tout calme.
+narrateur|Le grelot est petit, tout brillant.
+narrateur|Il tient au bout d'un fil rouge.
+enfant-f|Le grelot.
+maman|On attend, d'abord.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle n'agite pas le fil.
+narrateur|Le grelot reste silencieux.
+maitresse|Mila, tu peux.
+enfant-f|Cling.
+enfant-f|C'est mon tour.
+enfant-f|Le grelot chante.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|Et tu as sonné.
+papa|C'était le moment ?
+enfant-f|Oui, papa.
+narrateur|Le fil rouge redevient immobile.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11052,7 +11892,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu à la table. C'était le dessin. Elle a pris le grelot. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le fil rouge du grelot ne bouge plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11192,7 +12032,19 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu à la table.
+narrateur|C'était le dessin.
+narrateur|Elle a pris le grelot.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le fil rouge du grelot ne bouge plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11220,7 +12072,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Iris s'assoit près de la fenêtre. La lumière est claire. Elle lève la main. Elle attend. Puis elle parle. Je vois un oiseau.</t>
+          <t>La fenêtre est un peu embuée, en bas. Mila trace un chemin clair, du doigt. Dehors, un oiseau gris se pose sur la haie. Qui veut parler de l'oiseau ? Mila lève la main. Elle ne parle pas encore. D'abord attendre. Puis parler. J'attends. L'oiseau secoue une plume. Mila attend. Sa main reste en l'air, près de la vitre. Mila, c'est toi. Je vois un oiseau. Bravo. Tu as attendu. Puis parler. Très bien. Tu as levé la main ? Oui, maman. La vitre redevient un peu floue, en bas.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11360,8 +12212,27 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Iris s'assoit près de la fenêtre. La lumière est claire. Elle lève la main. Elle attend. Puis elle parle.
-narrateur|Je vois un oiseau.</t>
+          <t>narrateur|La fenêtre est un peu embuée, en bas.
+narrateur|Mila trace un chemin clair, du doigt.
+narrateur|Dehors, un oiseau gris se pose sur la haie.
+maitresse|Qui veut parler de l'oiseau ?
+narrateur|Mila lève la main.
+narrateur|Elle ne parle pas encore.
+maman|D'abord attendre.
+papa|Puis parler.
+enfant-f|J'attends.
+narrateur|L'oiseau secoue une plume.
+narrateur|Mila attend.
+narrateur|Sa main reste en l'air, près de la vitre.
+maitresse|Mila, c'est toi.
+enfant-f|Je vois un oiseau.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|Très bien.
+maman|Tu as levé la main ?
+enfant-f|Oui, maman.
+narrateur|La vitre redevient un peu floue, en bas.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11389,7 +12260,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Iris est près de la fenêtre. Que fait-elle d'abord ?</t>
+          <t>Mila est près de la fenêtre. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11545,7 +12416,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Iris est près de la fenêtre. Que fait-elle d'abord ?</t>
+          <t>narrateur|Mila est près de la fenêtre.
+maman|Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11573,7 +12445,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Iris a levé la main. Elle a attendu. Puis elle a parlé.</t>
+          <t>Elle attend. Puis parler. J'ai attendu. Puis j'ai parlé. Bravo, Mila. L'oiseau n'est plus sur la haie. Tu as fait du bon travail. Oui, papa.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11717,7 +12589,14 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Iris a levé la main. Elle a attendu. Puis elle a parlé.</t>
+          <t>papa|Elle attend.
+maman|Puis parler.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maitresse|Bravo, Mila.
+narrateur|L'oiseau n'est plus sur la haie.
+papa|Tu as fait du bon travail.
+enfant-f|Oui, papa.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11745,7 +12624,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>La fenêtre tient encore un morceau de ciel. On peut prendre l'histoire, la chanson, ou le dessin. Tu attends ton tour. Puis parler.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11913,7 +12792,10 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>narrateur|La fenêtre tient encore un morceau de ciel.
+papa|On peut prendre l'histoire, la chanson, ou le dessin.
+maman|Tu attends ton tour.
+papa|Puis parler.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11941,7 +12823,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Près de la fenêtre, on écoute l'histoire. Iris attend. Puis elle parle. Un oiseau passe.</t>
+          <t>La fenêtre tient encore un morceau de ciel. La maîtresse ouvre l'histoire. Le loup marche dans le bois, sur l'image. Les arbres sont verts, un peu sombres. Qui veut dire un mot ? Mila lève la main. Elle attend. D'abord attendre. Puis parler. J'attends. Un autre mot est dit, tout bas. Mila garde la main en l'air. Mila, à toi. Le loup est dans le bois. Bravo. Tu as attendu. Puis parler. C'est ça. Tu as levé la main ? Oui, maman. La page du loup reste ouverte, un moment.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12081,7 +12963,27 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Près de la fenêtre, on écoute l'histoire. Iris attend. Puis elle parle. Un oiseau passe.</t>
+          <t>narrateur|La fenêtre tient encore un morceau de ciel.
+narrateur|La maîtresse ouvre l'histoire.
+narrateur|Le loup marche dans le bois, sur l'image.
+narrateur|Les arbres sont verts, un peu sombres.
+maitresse|Qui veut dire un mot ?
+narrateur|Mila lève la main.
+narrateur|Elle attend.
+papa|D'abord attendre.
+maman|Puis parler.
+enfant-f|J'attends.
+narrateur|Un autre mot est dit, tout bas.
+narrateur|Mila garde la main en l'air.
+maitresse|Mila, à toi.
+enfant-f|Le loup est dans le bois.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|C'est ça.
+maman|Tu as levé la main ?
+enfant-f|Oui, maman.
+narrateur|La page du loup reste ouverte, un moment.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12109,7 +13011,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Le livre reste ouvert, sur le loup du bois. On peut prendre le crayon, le coussin, ou le grelot. Tu attends. Puis parler. Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12277,7 +13179,11 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Le livre reste ouvert, sur le loup du bois.
+maman|On peut prendre le crayon, le coussin, ou le grelot.
+papa|Tu attends.
+papa|Puis parler.
+maman|Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12305,7 +13211,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et l'histoire. Maman l'attend à la porte.</t>
+          <t>La fenêtre tient encore un morceau de ciel. Le livre reste ouvert, sur le loup du bois. Le crayon suit l'oiseau, sur la vitre embuée. Le crayon jaune sent un peu le bois. La mine est douce, déjà un peu ronde. Le crayon, s'il te plaît. Tu lèves la main, d'abord. Tu attends. Puis parler. Mila lève la main. Elle attend. Mila, tu peux prendre le crayon. Merci. Je parle maintenant. Le crayon est jaune. Bravo. Tu as attendu. Puis parler. C'est bien. Tu as fini d'attendre ton tour ? Oui, papa. Un petit trait jaune reste sur le papier. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12445,7 +13351,29 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et l'histoire. Maman l'attend à la porte.</t>
+          <t>narrateur|La fenêtre tient encore un morceau de ciel.
+narrateur|Le livre reste ouvert, sur le loup du bois.
+narrateur|Le crayon suit l'oiseau, sur la vitre embuée.
+narrateur|Le crayon jaune sent un peu le bois.
+narrateur|La mine est douce, déjà un peu ronde.
+enfant-f|Le crayon, s'il te plaît.
+maman|Tu lèves la main, d'abord.
+papa|Tu attends.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle attend.
+maitresse|Mila, tu peux prendre le crayon.
+enfant-f|Merci.
+enfant-f|Je parle maintenant.
+enfant-f|Le crayon est jaune.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|C'est bien.
+papa|Tu as fini d'attendre ton tour ?
+enfant-f|Oui, papa.
+narrateur|Un petit trait jaune reste sur le papier.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12473,7 +13401,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu près de la fenêtre. C'était l'histoire. Elle a pris le crayon. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le crayon jaune a un trait, tout mince, au bout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12613,7 +13541,19 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu près de la fenêtre.
+narrateur|C'était l'histoire.
+narrateur|Elle a pris le crayon.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le crayon jaune a un trait, tout mince, au bout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12641,7 +13581,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et l'histoire. Maman l'attend à la porte.</t>
+          <t>La fenêtre tient encore un morceau de ciel. Le livre reste ouvert, sur le loup du bois. Le coussin est près de la fenêtre, pendant le loup. Le coussin bleu est mou, un peu lourd. Il sent la classe, et un peu le savon. Le coussin. Tu attends, d'abord. Puis parler. Mila lève la main. Le coussin attend aussi. Elle ne le prend pas encore. Mila, c'est toi. Je m'assois. Puis je parle. Le coussin est doux. Bravo. Tu as attendu. Puis parler. Oui. Tu es bien, là ? Oui, maman. Le coussin s'enfonce un peu, sous elle. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12781,7 +13721,29 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et l'histoire. Maman l'attend à la porte.</t>
+          <t>narrateur|La fenêtre tient encore un morceau de ciel.
+narrateur|Le livre reste ouvert, sur le loup du bois.
+narrateur|Le coussin est près de la fenêtre, pendant le loup.
+narrateur|Le coussin bleu est mou, un peu lourd.
+narrateur|Il sent la classe, et un peu le savon.
+enfant-f|Le coussin.
+papa|Tu attends, d'abord.
+maman|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Le coussin attend aussi.
+narrateur|Elle ne le prend pas encore.
+maitresse|Mila, c'est toi.
+enfant-f|Je m'assois.
+enfant-f|Puis je parle.
+enfant-f|Le coussin est doux.
+maman|Bravo.
+maman|Tu as attendu.
+papa|Puis parler.
+papa|Oui.
+maman|Tu es bien, là ?
+enfant-f|Oui, maman.
+narrateur|Le coussin s'enfonce un peu, sous elle.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12809,7 +13771,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu près de la fenêtre. C'était l'histoire. Elle a pris le coussin. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le coussin bleu garde encore la forme de Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12949,7 +13911,19 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu près de la fenêtre.
+narrateur|C'était l'histoire.
+narrateur|Elle a pris le coussin.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le coussin bleu garde encore la forme de Mila.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12977,7 +13951,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et l'histoire. Maman l'attend à la porte.</t>
+          <t>La fenêtre tient encore un morceau de ciel. Le livre reste ouvert, sur le loup du bois. Le grelot ne sonne pas. L'oiseau s'envole d'abord. Le grelot est petit, tout brillant. Il tient au bout d'un fil rouge. Le grelot. On attend, d'abord. Puis parler. Mila lève la main. Elle n'agite pas le fil. Le grelot reste silencieux. Mila, tu peux. Cling. C'est mon tour. Le grelot chante. Bravo. Tu as attendu. Puis parler. Et tu as sonné. C'était le moment ? Oui, papa. Le fil rouge redevient immobile. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13117,7 +14091,30 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et l'histoire. Maman l'attend à la porte.</t>
+          <t>narrateur|La fenêtre tient encore un morceau de ciel.
+narrateur|Le livre reste ouvert, sur le loup du bois.
+narrateur|Le grelot ne sonne pas.
+narrateur|L'oiseau s'envole d'abord.
+narrateur|Le grelot est petit, tout brillant.
+narrateur|Il tient au bout d'un fil rouge.
+enfant-f|Le grelot.
+maman|On attend, d'abord.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle n'agite pas le fil.
+narrateur|Le grelot reste silencieux.
+maitresse|Mila, tu peux.
+enfant-f|Cling.
+enfant-f|C'est mon tour.
+enfant-f|Le grelot chante.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|Et tu as sonné.
+papa|C'était le moment ?
+enfant-f|Oui, papa.
+narrateur|Le fil rouge redevient immobile.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13145,7 +14142,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu près de la fenêtre. C'était l'histoire. Elle a pris le grelot. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le fil rouge du grelot ne bouge plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13285,7 +14282,19 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu près de la fenêtre.
+narrateur|C'était l'histoire.
+narrateur|Elle a pris le grelot.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le fil rouge du grelot ne bouge plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13313,7 +14322,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>On chante près de la lumière. Iris attend. Puis elle parle. C'est clair.</t>
+          <t>La fenêtre tient encore un morceau de ciel. On chante tout doux, dans la classe. La chanson parle d'une pluie, d'un toit. Mila connaît un mot. Elle lève la main. Tu attends ton tour. Puis parler. J'attends. La chanson continue. Mila n'interrompt pas. Ses pieds restent sages, sous elle. Mila, tu peux dire le mot. Le toit. C'est clair. Bravo. Tu as su attendre. Puis parler. Bien. C'était ton tour ? Oui, papa. Un dernier air reste, tout petit, dans l'air.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13453,8 +14462,27 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|On chante près de la lumière. Iris attend. Puis elle parle.
-narrateur|C'est clair.</t>
+          <t>narrateur|La fenêtre tient encore un morceau de ciel.
+narrateur|On chante tout doux, dans la classe.
+narrateur|La chanson parle d'une pluie, d'un toit.
+narrateur|Mila connaît un mot.
+narrateur|Elle lève la main.
+maman|Tu attends ton tour.
+papa|Puis parler.
+enfant-f|J'attends.
+narrateur|La chanson continue.
+narrateur|Mila n'interrompt pas.
+narrateur|Ses pieds restent sages, sous elle.
+maitresse|Mila, tu peux dire le mot.
+enfant-f|Le toit.
+enfant-f|C'est clair.
+papa|Bravo.
+papa|Tu as su attendre.
+maman|Puis parler.
+maman|Bien.
+papa|C'était ton tour ?
+enfant-f|Oui, papa.
+narrateur|Un dernier air reste, tout petit, dans l'air.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13482,7 +14510,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Un air tout petit reste dans la classe. On peut prendre le crayon, le coussin, ou le grelot. Tu attends. Puis parler. Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13650,7 +14678,11 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Un air tout petit reste dans la classe.
+maman|On peut prendre le crayon, le coussin, ou le grelot.
+papa|Tu attends.
+papa|Puis parler.
+maman|Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13678,7 +14710,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et la chanson. Maman l'attend à la porte.</t>
+          <t>La fenêtre tient encore un morceau de ciel. Un air tout petit reste dans la classe. Le crayon dessine un toit, contre la lumière. Le crayon jaune sent un peu le bois. La mine est douce, déjà un peu ronde. Le crayon, s'il te plaît. Tu lèves la main, d'abord. Tu attends. Puis parler. Mila lève la main. Elle attend. Mila, tu peux prendre le crayon. Merci. Je parle maintenant. Le crayon est jaune. Bravo. Tu as attendu. Puis parler. C'est bien. Tu as fini d'attendre ton tour ? Oui, papa. Un petit trait jaune reste sur le papier. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13818,7 +14850,29 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et la chanson. Maman l'attend à la porte.</t>
+          <t>narrateur|La fenêtre tient encore un morceau de ciel.
+narrateur|Un air tout petit reste dans la classe.
+narrateur|Le crayon dessine un toit, contre la lumière.
+narrateur|Le crayon jaune sent un peu le bois.
+narrateur|La mine est douce, déjà un peu ronde.
+enfant-f|Le crayon, s'il te plaît.
+maman|Tu lèves la main, d'abord.
+papa|Tu attends.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle attend.
+maitresse|Mila, tu peux prendre le crayon.
+enfant-f|Merci.
+enfant-f|Je parle maintenant.
+enfant-f|Le crayon est jaune.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|C'est bien.
+papa|Tu as fini d'attendre ton tour ?
+enfant-f|Oui, papa.
+narrateur|Un petit trait jaune reste sur le papier.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13846,7 +14900,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu près de la fenêtre. C'était la chanson. Elle a pris le crayon. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le crayon jaune a un trait, tout mince, au bout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13986,7 +15040,19 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu près de la fenêtre.
+narrateur|C'était la chanson.
+narrateur|Elle a pris le crayon.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le crayon jaune a un trait, tout mince, au bout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14014,7 +15080,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et la chanson. Maman l'attend à la porte.</t>
+          <t>La fenêtre tient encore un morceau de ciel. Un air tout petit reste dans la classe. Le coussin est tiède, sous la chanson de la pluie. Le coussin bleu est mou, un peu lourd. Il sent la classe, et un peu le savon. Le coussin. Tu attends, d'abord. Puis parler. Mila lève la main. Le coussin attend aussi. Elle ne le prend pas encore. Mila, c'est toi. Je m'assois. Puis je parle. Le coussin est doux. Bravo. Tu as attendu. Puis parler. Oui. Tu es bien, là ? Oui, maman. Le coussin s'enfonce un peu, sous elle. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14154,7 +15220,29 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et la chanson. Maman l'attend à la porte.</t>
+          <t>narrateur|La fenêtre tient encore un morceau de ciel.
+narrateur|Un air tout petit reste dans la classe.
+narrateur|Le coussin est tiède, sous la chanson de la pluie.
+narrateur|Le coussin bleu est mou, un peu lourd.
+narrateur|Il sent la classe, et un peu le savon.
+enfant-f|Le coussin.
+papa|Tu attends, d'abord.
+maman|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Le coussin attend aussi.
+narrateur|Elle ne le prend pas encore.
+maitresse|Mila, c'est toi.
+enfant-f|Je m'assois.
+enfant-f|Puis je parle.
+enfant-f|Le coussin est doux.
+maman|Bravo.
+maman|Tu as attendu.
+papa|Puis parler.
+papa|Oui.
+maman|Tu es bien, là ?
+enfant-f|Oui, maman.
+narrateur|Le coussin s'enfonce un peu, sous elle.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14182,7 +15270,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu près de la fenêtre. C'était la chanson. Elle a pris le coussin. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le coussin bleu garde encore la forme de Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14322,7 +15410,19 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu près de la fenêtre.
+narrateur|C'était la chanson.
+narrateur|Elle a pris le coussin.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le coussin bleu garde encore la forme de Mila.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14350,7 +15450,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et la chanson. Maman l'attend à la porte.</t>
+          <t>La fenêtre tient encore un morceau de ciel. Un air tout petit reste dans la classe. Le grelot attend que la vitre redevienne claire. Le grelot est petit, tout brillant. Il tient au bout d'un fil rouge. Le grelot. On attend, d'abord. Puis parler. Mila lève la main. Elle n'agite pas le fil. Le grelot reste silencieux. Mila, tu peux. Cling. C'est mon tour. Le grelot chante. Bravo. Tu as attendu. Puis parler. Et tu as sonné. C'était le moment ? Oui, papa. Le fil rouge redevient immobile. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14490,7 +15590,29 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et la chanson. Maman l'attend à la porte.</t>
+          <t>narrateur|La fenêtre tient encore un morceau de ciel.
+narrateur|Un air tout petit reste dans la classe.
+narrateur|Le grelot attend que la vitre redevienne claire.
+narrateur|Le grelot est petit, tout brillant.
+narrateur|Il tient au bout d'un fil rouge.
+enfant-f|Le grelot.
+maman|On attend, d'abord.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle n'agite pas le fil.
+narrateur|Le grelot reste silencieux.
+maitresse|Mila, tu peux.
+enfant-f|Cling.
+enfant-f|C'est mon tour.
+enfant-f|Le grelot chante.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|Et tu as sonné.
+papa|C'était le moment ?
+enfant-f|Oui, papa.
+narrateur|Le fil rouge redevient immobile.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14518,7 +15640,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu près de la fenêtre. C'était la chanson. Elle a pris le grelot. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le fil rouge du grelot ne bouge plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14658,7 +15780,19 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu près de la fenêtre.
+narrateur|C'était la chanson.
+narrateur|Elle a pris le grelot.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le fil rouge du grelot ne bouge plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14686,7 +15820,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Iris dessine la fenêtre. Elle attend. Puis elle parle. J'ai fini le toit.</t>
+          <t>La fenêtre tient encore un morceau de ciel. Un papier blanc attend sur le bois. Une gomme sent le caoutchouc, tout près. Mila a une couleur dans la tête. Elle lève la main. Il faut attendre. Puis parler. J'attends. Quelqu'un nomme le rouge, d'abord. Mila attend. Sa main ne descend pas. Mila, c'est ton tour. Moi, le bleu. Bravo. Tu as attendu. Puis parler. Très bien. Tu as dit le bleu ? Oui, maman. Un trait bleu commence, tout mince, sur le papier.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14826,8 +15960,26 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Iris dessine la fenêtre. Elle attend. Puis elle parle.
-narrateur|J'ai fini le toit.</t>
+          <t>narrateur|La fenêtre tient encore un morceau de ciel.
+narrateur|Un papier blanc attend sur le bois.
+narrateur|Une gomme sent le caoutchouc, tout près.
+narrateur|Mila a une couleur dans la tête.
+narrateur|Elle lève la main.
+papa|Il faut attendre.
+maman|Puis parler.
+enfant-f|J'attends.
+narrateur|Quelqu'un nomme le rouge, d'abord.
+narrateur|Mila attend.
+narrateur|Sa main ne descend pas.
+maitresse|Mila, c'est ton tour.
+enfant-f|Moi, le bleu.
+maman|Bravo.
+maman|Tu as attendu.
+papa|Puis parler.
+papa|Très bien.
+maman|Tu as dit le bleu ?
+enfant-f|Oui, maman.
+narrateur|Un trait bleu commence, tout mince, sur le papier.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14855,7 +16007,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Le papier blanc attend encore une couleur. On peut prendre le crayon, le coussin, ou le grelot. Tu attends. Puis parler. Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15023,7 +16175,11 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Le papier blanc attend encore une couleur.
+maman|On peut prendre le crayon, le coussin, ou le grelot.
+papa|Tu attends.
+papa|Puis parler.
+maman|Ensuite c'est ton tour.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15051,7 +16207,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et le dessin. Maman l'attend à la porte.</t>
+          <t>La fenêtre tient encore un morceau de ciel. Le papier blanc attend encore une couleur. Le crayon jaune copie l'oiseau, sur le papier. Le crayon jaune sent un peu le bois. La mine est douce, déjà un peu ronde. Le crayon, s'il te plaît. Tu lèves la main, d'abord. Tu attends. Puis parler. Mila lève la main. Elle attend. Mila, tu peux prendre le crayon. Merci. Je parle maintenant. Le crayon est jaune. Bravo. Tu as attendu. Puis parler. C'est bien. Tu as fini d'attendre ton tour ? Oui, papa. Un petit trait jaune reste sur le papier. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15191,7 +16347,29 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Léa a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et le dessin. Maman l'attend à la porte.</t>
+          <t>narrateur|La fenêtre tient encore un morceau de ciel.
+narrateur|Le papier blanc attend encore une couleur.
+narrateur|Le crayon jaune copie l'oiseau, sur le papier.
+narrateur|Le crayon jaune sent un peu le bois.
+narrateur|La mine est douce, déjà un peu ronde.
+enfant-f|Le crayon, s'il te plaît.
+maman|Tu lèves la main, d'abord.
+papa|Tu attends.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle attend.
+maitresse|Mila, tu peux prendre le crayon.
+enfant-f|Merci.
+enfant-f|Je parle maintenant.
+enfant-f|Le crayon est jaune.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|C'est bien.
+papa|Tu as fini d'attendre ton tour ?
+enfant-f|Oui, papa.
+narrateur|Un petit trait jaune reste sur le papier.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15219,7 +16397,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu près de la fenêtre. C'était le dessin. Elle a pris le crayon. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le crayon jaune a un trait, tout mince, au bout. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15359,7 +16537,19 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu près de la fenêtre.
+narrateur|C'était le dessin.
+narrateur|Elle a pris le crayon.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le crayon jaune a un trait, tout mince, au bout.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15387,7 +16577,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et le dessin. Maman l'attend à la porte.</t>
+          <t>La fenêtre tient encore un morceau de ciel. Le papier blanc attend encore une couleur. Le coussin bleu a un carré de soleil, près de la vitre. Le coussin bleu est mou, un peu lourd. Il sent la classe, et un peu le savon. Le coussin. Tu attends, d'abord. Puis parler. Mila lève la main. Le coussin attend aussi. Elle ne le prend pas encore. Mila, c'est toi. Je m'assois. Puis je parle. Le coussin est doux. Bravo. Tu as attendu. Puis parler. Oui. Tu es bien, là ? Oui, maman. Le coussin s'enfonce un peu, sous elle. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15527,7 +16717,29 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Tom a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et le dessin. Maman l'attend à la porte.</t>
+          <t>narrateur|La fenêtre tient encore un morceau de ciel.
+narrateur|Le papier blanc attend encore une couleur.
+narrateur|Le coussin bleu a un carré de soleil, près de la vitre.
+narrateur|Le coussin bleu est mou, un peu lourd.
+narrateur|Il sent la classe, et un peu le savon.
+enfant-f|Le coussin.
+papa|Tu attends, d'abord.
+maman|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Le coussin attend aussi.
+narrateur|Elle ne le prend pas encore.
+maitresse|Mila, c'est toi.
+enfant-f|Je m'assois.
+enfant-f|Puis je parle.
+enfant-f|Le coussin est doux.
+maman|Bravo.
+maman|Tu as attendu.
+papa|Puis parler.
+papa|Oui.
+maman|Tu es bien, là ?
+enfant-f|Oui, maman.
+narrateur|Le coussin s'enfonce un peu, sous elle.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15555,7 +16767,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu près de la fenêtre. C'était le dessin. Elle a pris le coussin. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le coussin bleu garde encore la forme de Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15695,7 +16907,19 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu près de la fenêtre.
+narrateur|C'était le dessin.
+narrateur|Elle a pris le coussin.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le coussin bleu garde encore la forme de Mila.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15723,7 +16947,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et le dessin. Maman l'attend à la porte.</t>
+          <t>La fenêtre tient encore un morceau de ciel. Le papier blanc attend encore une couleur. Le grelot cling, tout doux, quand l'oiseau n'est plus là. Le grelot est petit, tout brillant. Il tient au bout d'un fil rouge. Le grelot. On attend, d'abord. Puis parler. Mila lève la main. Elle n'agite pas le fil. Le grelot reste silencieux. Mila, tu peux. Cling. C'est mon tour. Le grelot chante. Bravo. Tu as attendu. Puis parler. Et tu as sonné. C'était le moment ? Oui, papa. Le fil rouge redevient immobile. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15863,7 +17087,29 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Sami a écouté. Iris a attendu. Puis elle a parlé. C'était la fenêtre et le dessin. Maman l'attend à la porte.</t>
+          <t>narrateur|La fenêtre tient encore un morceau de ciel.
+narrateur|Le papier blanc attend encore une couleur.
+narrateur|Le grelot cling, tout doux, quand l'oiseau n'est plus là.
+narrateur|Le grelot est petit, tout brillant.
+narrateur|Il tient au bout d'un fil rouge.
+enfant-f|Le grelot.
+maman|On attend, d'abord.
+papa|Puis parler.
+narrateur|Mila lève la main.
+narrateur|Elle n'agite pas le fil.
+narrateur|Le grelot reste silencieux.
+maitresse|Mila, tu peux.
+enfant-f|Cling.
+enfant-f|C'est mon tour.
+enfant-f|Le grelot chante.
+papa|Bravo.
+papa|Tu as attendu.
+maman|Puis parler.
+maman|Et tu as sonné.
+papa|C'était le moment ?
+enfant-f|Oui, papa.
+narrateur|Le fil rouge redevient immobile.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15891,7 +17137,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a attendu près de la fenêtre. C'était le dessin. Elle a pris le grelot. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. D'abord attendre. Puis parler. Oui, maman. Le fil rouge du grelot ne bouge plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16031,7 +17277,19 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a attendu près de la fenêtre.
+narrateur|C'était le dessin.
+narrateur|Elle a pris le grelot.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|D'abord attendre.
+maman|Puis parler.
+enfant-f|Oui, maman.
+narrateur|Le fil rouge du grelot ne bouge plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16053,7 +17311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16161,6 +17419,13 @@
       <c r="A15" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-006.xlsx
+++ b/stories/arbres/TREE-COL-006.xlsx
@@ -10110,17 +10110,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Le rayon du vestiaire traverse le coussin, puis s'en va. La virgule a failli s'étouffer, sous le bleu. Elle chante, sur nos genoux. Deux chansons, un bois nu. Nina tapote, plus léger. Papa plie l'écharpe, le fil d'or au bord. Maman a plié l'écharpe, le fil d'or caché.</t>
+          <t>Le rayon du vestiaire traverse le coussin, puis s'en va. La virgule a failli s'étouffer, sous le bleu. Elle chante, sur nos genoux. Deux chansons, un bois nu. Nina tapote, plus léger. Papa raccroche le ciré, au crochet voisin. Maman a plié l'écharpe, le fil d'or caché.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le rayon du vestiaire traverse le coussin, puis s'en va. La virgule a failli s'étouffer, sous le bleu. Elle chante, sur nos genoux. Deux chansons, un bois nu. Nina tapote, plus léger. Papa plie l'écharpe, le fil d'or au bord. Maman a plié l'écharpe, le fil d'or caché.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le rayon du vestiaire traverse le coussin, puis s'en va. La virgule a failli s'étouffer, sous le bleu. Elle chante, sur nos genoux. Deux chansons, un bois nu. Nina tapote, plus léger. Papa raccroche le ciré, au crochet voisin. Maman a plié l'écharpe, le fil d'or caché.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le rayon du vestiaire traverse le coussin, puis s'en va. La virgule a failli s'étouffer, sous le bleu. Elle chante, sur nos genoux. Deux chansons, un bois nu. Nina tapote, plus léger. Papa plie l'écharpe, le fil d'or au bord. Maman a plié l'écharpe, le fil d'or caché.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le rayon du vestiaire traverse le coussin, puis s'en va. La virgule a failli s'étouffer, sous le bleu. Elle chante, sur nos genoux. Deux chansons, un bois nu. Nina tapote, plus léger. Papa raccroche le ciré, au crochet voisin. Maman a plié l'écharpe, le fil d'or caché.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -10263,7 +10263,7 @@
 enfant-f|Elle chante, sur nos genoux.
 maman|Deux chansons, un bois nu.
 narrateur|Nina tapote, plus léger.
-narrateur|Papa plie l'écharpe, le fil d'or au bord.
+narrateur|Papa raccroche le ciré, au crochet voisin.
 narrateur|Maman a plié l'écharpe, le fil d'or caché.</t>
         </is>
       </c>
@@ -13326,17 +13326,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Près de la fenêtre, Mila veut tracer l'or sur le verre. La virgule, sur la vitre ! Le ciel, sur la vitre ! Le crayon glisse, et un trait rate le ciel. Nina grogne, tout bas. Mila retire la mine, sans frotter. Dans le miroir, la vraie virgule d'or tient. Toi le ciel, dans l'eau. Toi l'or, sur le papier, pas sur le verre. La vitre a gardé un trait pâle, souvenir. Le livre a retrouvé le loup, au sec. Mila dessine l'or sur une feuille, loin du froid. Nina dit le ciel, en regardant la flaque. Le nuage de l'eau a cessé de trembler.</t>
+          <t>Près de la fenêtre, Mila veut tracer l'or sur le verre. La virgule, sur la vitre ! Le ciel, sur la vitre ! Le crayon glisse, et un trait rate le ciel. Nina souffle, tout bas. Mila retire la mine, sans frotter. Dans le miroir, la vraie virgule d'or tient. Toi le ciel, dans l'eau. Toi l'or, sur le papier, pas sur le verre. La vitre a gardé un trait pâle, souvenir. Le livre a retrouvé le loup, au sec. Mila dessine l'or sur une feuille, loin du froid. Nina dit le ciel, en regardant la flaque. Le nuage de l'eau a cessé de trembler.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Près de la fenêtre, Mila veut tracer l'or sur le verre. La virgule, sur la vitre ! Le ciel, sur la vitre ! Le crayon glisse, et un trait rate le ciel. Nina grogne, tout bas. Mila retire la mine, sans frotter. Dans le miroir, la vraie &lt;emphasis level="moderate"&gt;virgule d'or&lt;/emphasis&gt; tient. Toi le ciel, dans l'eau. Toi l'or, sur le papier, pas sur le verre. La vitre a gardé un trait pâle, souvenir. Le livre a retrouvé le loup, au sec. Mila dessine l'or sur une feuille, loin du froid. Nina dit le ciel, en regardant la flaque. Le nuage de l'eau a cessé de trembler.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Près de la fenêtre, Mila veut tracer l'or sur le verre. La virgule, sur la vitre ! Le ciel, sur la vitre ! Le crayon glisse, et un trait rate le ciel. Nina souffle, tout bas. Mila retire la mine, sans frotter. Dans le miroir, la vraie &lt;emphasis level="moderate"&gt;virgule d'or&lt;/emphasis&gt; tient. Toi le ciel, dans l'eau. Toi l'or, sur le papier, pas sur le verre. La vitre a gardé un trait pâle, souvenir. Le livre a retrouvé le loup, au sec. Mila dessine l'or sur une feuille, loin du froid. Nina dit le ciel, en regardant la flaque. Le nuage de l'eau a cessé de trembler.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Près de la fenêtre, Mila veut tracer l'or sur le verre. La virgule, sur la vitre ! Le ciel, sur la vitre ! Le crayon glisse, et un trait rate le ciel. Nina grogne, tout bas. Mila retire la mine, sans frotter. Dans le miroir, la vraie &lt;emphasis&gt;virgule d'or&lt;/emphasis&gt; tient. Toi le ciel, dans l'eau. Toi l'or, sur le papier, pas sur le verre. La vitre a gardé un trait pâle, souvenir. Le livre a retrouvé le loup, au sec. Mila dessine l'or sur une feuille, loin du froid. Nina dit le ciel, en regardant la flaque. Le nuage de l'eau a cessé de trembler. [pause]</t>
+          <t>Près de la fenêtre, Mila veut tracer l'or sur le verre. La virgule, sur la vitre ! Le ciel, sur la vitre ! Le crayon glisse, et un trait rate le ciel. Nina souffle, tout bas. Mila retire la mine, sans frotter. Dans le miroir, la vraie &lt;emphasis&gt;virgule d'or&lt;/emphasis&gt; tient. Toi le ciel, dans l'eau. Toi l'or, sur le papier, pas sur le verre. La vitre a gardé un trait pâle, souvenir. Le livre a retrouvé le loup, au sec. Mila dessine l'or sur une feuille, loin du froid. Nina dit le ciel, en regardant la flaque. Le nuage de l'eau a cessé de trembler. [pause]</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -13474,7 +13474,7 @@
 enfant-f|La virgule, sur la vitre !
 copine|Le ciel, sur la vitre !
 narrateur|Le crayon glisse, et un trait rate le ciel.
-narrateur|Nina grogne, tout bas.
+narrateur|Nina souffle, tout bas.
 narrateur|Mila retire la mine, sans frotter.
 narrateur|Dans le miroir, la vraie virgule d'or tient.
 enfant-f|Toi le ciel, dans l'eau.
@@ -17477,7 +17477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17604,6 +17604,13 @@
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
